--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.82636072163533</v>
+        <v>5.821783617265741</v>
       </c>
       <c r="D2" t="n">
-        <v>36.01404734690436</v>
+        <v>5.852282693871958</v>
       </c>
       <c r="E2" t="n">
-        <v>6.700814434012515</v>
+        <v>1.088882345527034</v>
       </c>
       <c r="F2" t="n">
-        <v>7.692029382897923</v>
+        <v>1.249954774720913</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.06788682215237</v>
+        <v>6.67353160859976</v>
       </c>
       <c r="D3" t="n">
-        <v>41.7396027183919</v>
+        <v>6.782685441738684</v>
       </c>
       <c r="E3" t="n">
-        <v>6.700814434012515</v>
+        <v>1.088882345527034</v>
       </c>
       <c r="F3" t="n">
-        <v>7.692029382897923</v>
+        <v>1.249954774720913</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.42060825572271</v>
+        <v>7.218348841554941</v>
       </c>
       <c r="D4" t="n">
-        <v>43.92878725765242</v>
+        <v>7.138427929368519</v>
       </c>
       <c r="E4" t="n">
-        <v>6.700814434012515</v>
+        <v>1.088882345527034</v>
       </c>
       <c r="F4" t="n">
-        <v>7.692029382897923</v>
+        <v>1.249954774720913</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.40142295034784</v>
+        <v>5.265231229431524</v>
       </c>
       <c r="D5" t="n">
-        <v>32.01363643438395</v>
+        <v>5.202215920587392</v>
       </c>
       <c r="E5" t="n">
-        <v>6.700814434012515</v>
+        <v>1.088882345527034</v>
       </c>
       <c r="F5" t="n">
-        <v>7.692029382897923</v>
+        <v>1.249954774720913</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.36455880860071</v>
+        <v>7.696740806397616</v>
       </c>
       <c r="D6" t="n">
-        <v>46.75899794888124</v>
+        <v>7.598337166693202</v>
       </c>
       <c r="E6" t="n">
-        <v>6.700814434012515</v>
+        <v>1.088882345527034</v>
       </c>
       <c r="F6" t="n">
-        <v>7.692029382897923</v>
+        <v>1.249954774720913</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.17056229566886</v>
+        <v>5.715216373046189</v>
       </c>
       <c r="D7" t="n">
-        <v>35.76135115705253</v>
+        <v>5.811219563021036</v>
       </c>
       <c r="E7" t="n">
-        <v>6.700814434012515</v>
+        <v>1.088882345527034</v>
       </c>
       <c r="F7" t="n">
-        <v>7.692029382897923</v>
+        <v>1.249954774720913</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.24656888292242</v>
+        <v>7.515067443474893</v>
       </c>
       <c r="D8" t="n">
-        <v>45.5823046218874</v>
+        <v>7.407124501056703</v>
       </c>
       <c r="E8" t="n">
-        <v>6.700814434012515</v>
+        <v>1.088882345527034</v>
       </c>
       <c r="F8" t="n">
-        <v>7.692029382897923</v>
+        <v>1.249954774720913</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.69591381327346</v>
+        <v>7.100585994656937</v>
       </c>
       <c r="D9" t="n">
-        <v>24.25386567126981</v>
+        <v>3.941253171581344</v>
       </c>
       <c r="E9" t="n">
-        <v>6.700814434012515</v>
+        <v>1.088882345527034</v>
       </c>
       <c r="F9" t="n">
-        <v>7.692029382897923</v>
+        <v>1.249954774720913</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.82854758522226</v>
+        <v>4.034638982598617</v>
       </c>
       <c r="D10" t="n">
-        <v>24.22925266560295</v>
+        <v>3.937253558160479</v>
       </c>
       <c r="E10" t="n">
-        <v>6.700814434012515</v>
+        <v>1.088882345527034</v>
       </c>
       <c r="F10" t="n">
-        <v>7.692029382897923</v>
+        <v>1.249954774720913</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>37.62329210013641</v>
+        <v>6.113784966272167</v>
       </c>
       <c r="D11" t="n">
-        <v>37.17181595836959</v>
+        <v>6.040420093235059</v>
       </c>
       <c r="E11" t="n">
-        <v>6.700814434012515</v>
+        <v>1.088882345527034</v>
       </c>
       <c r="F11" t="n">
-        <v>7.692029382897923</v>
+        <v>1.249954774720913</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
